--- a/a/links_ cfe.xlsx
+++ b/a/links_ cfe.xlsx
@@ -7,8 +7,8 @@
     <workbookView xWindow="0" yWindow="120" windowWidth="19140" windowHeight="6840"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
-    <sheet name="Лист2" sheetId="2" r:id="rId2"/>
+    <sheet name="links" sheetId="1" r:id="rId1"/>
+    <sheet name="code" sheetId="2" r:id="rId2"/>
     <sheet name="Лист3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="144525"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="28">
   <si>
     <t>insert_url</t>
   </si>
@@ -30,9 +30,6 @@
     <t>external_link</t>
   </si>
   <si>
-    <t>https://www.g20yea.com/</t>
-  </si>
-  <si>
     <t>https://www.genglobal.org/startup-huddle</t>
   </si>
   <si>
@@ -60,9 +57,6 @@
     <t>program</t>
   </si>
   <si>
-    <t>Type</t>
-  </si>
-  <si>
     <t>goals</t>
   </si>
   <si>
@@ -90,13 +84,22 @@
     <t>/goals/support-entrepreneurship</t>
   </si>
   <si>
-    <t>/goals/mentor-business</t>
-  </si>
-  <si>
     <t>https://www.fasttrac.org</t>
   </si>
   <si>
-    <t>key_words</t>
+    <t>/goals/mentoring-business</t>
+  </si>
+  <si>
+    <t>topic</t>
+  </si>
+  <si>
+    <t>https://www.g20yea.com</t>
+  </si>
+  <si>
+    <t>partner</t>
+  </si>
+  <si>
+    <t>topic_name</t>
   </si>
 </sst>
 </file>
@@ -435,7 +438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.453125" customWidth="1"/>
@@ -445,7 +448,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -454,155 +457,160 @@
         <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/a/links_ cfe.xlsx
+++ b/a/links_ cfe.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="22">
   <si>
     <t>insert_url</t>
   </si>
@@ -27,18 +27,9 @@
     <t>/programs/global-entrepreneurship-week</t>
   </si>
   <si>
-    <t>external_link</t>
-  </si>
-  <si>
-    <t>https://www.genglobal.org/startup-huddle</t>
-  </si>
-  <si>
     <t>/programs/young-entrepreneurs-alliance</t>
   </si>
   <si>
-    <t>https://www.genglobal.org/gew</t>
-  </si>
-  <si>
     <t>/programs/dynamic-entrepreneurship-classroom</t>
   </si>
   <si>
@@ -84,22 +75,13 @@
     <t>/goals/support-entrepreneurship</t>
   </si>
   <si>
-    <t>https://www.fasttrac.org</t>
-  </si>
-  <si>
     <t>/goals/mentoring-business</t>
   </si>
   <si>
     <t>topic</t>
   </si>
   <si>
-    <t>https://www.g20yea.com</t>
-  </si>
-  <si>
     <t>partner</t>
-  </si>
-  <si>
-    <t>topic_name</t>
   </si>
 </sst>
 </file>
@@ -438,179 +420,160 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.453125" customWidth="1"/>
     <col min="2" max="2" width="37.453125" customWidth="1"/>
-    <col min="3" max="3" width="36.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
         <v>14</v>
       </c>
-      <c r="C9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>10</v>
       </c>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B15" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>10</v>
       </c>
-      <c r="B12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="B16" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/a/links_ cfe.xlsx
+++ b/a/links_ cfe.xlsx
@@ -4,11 +4,11 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="120" windowWidth="19140" windowHeight="6840"/>
+    <workbookView xWindow="0" yWindow="120" windowWidth="19140" windowHeight="6840" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="links" sheetId="1" r:id="rId1"/>
-    <sheet name="code" sheetId="2" r:id="rId2"/>
+    <sheet name="statistic" sheetId="2" r:id="rId2"/>
     <sheet name="Лист3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="144525"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
   <si>
     <t>insert_url</t>
   </si>
@@ -82,6 +82,30 @@
   </si>
   <si>
     <t>partner</t>
+  </si>
+  <si>
+    <t>Url</t>
+  </si>
+  <si>
+    <t>start_date</t>
+  </si>
+  <si>
+    <t>stat1</t>
+  </si>
+  <si>
+    <t>stat2</t>
+  </si>
+  <si>
+    <t>stat3</t>
+  </si>
+  <si>
+    <t>hero_title</t>
+  </si>
+  <si>
+    <t>sub_title</t>
+  </si>
+  <si>
+    <t>Participants</t>
   </si>
 </sst>
 </file>
@@ -583,9 +607,155 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="3" width="17.54296875" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" customWidth="1"/>
+    <col min="8" max="8" width="11.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" t="str">
+        <f>links!B2</f>
+        <v>/programs/startup-huddle</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" t="str">
+        <f>links!B3</f>
+        <v>/programs/global-entrepreneurship-week</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" t="str">
+        <f>links!B4</f>
+        <v>/programs/young-entrepreneurs-alliance</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" t="str">
+        <f>links!B5</f>
+        <v>/programs/dynamic-entrepreneurship-classroom</v>
+      </c>
+      <c r="E5">
+        <v>460</v>
+      </c>
+      <c r="F5">
+        <v>80</v>
+      </c>
+      <c r="G5">
+        <v>30</v>
+      </c>
+      <c r="H5">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" t="str">
+        <f>links!B6</f>
+        <v>/programs/scaleup-acceleration-program</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" t="str">
+        <f>links!B7</f>
+        <v>/programs/scaleup-club</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" t="str">
+        <f>links!B8</f>
+        <v>/programs/startup-club</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" t="str">
+        <f>links!B9</f>
+        <v>/programs/fasttrac</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" t="str">
+        <f>links!B10</f>
+        <v>/categories/acceleration-programs</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" t="str">
+        <f>links!B11</f>
+        <v>/categories/startup-programs</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" t="str">
+        <f>links!B12</f>
+        <v>/categories/educational-programs</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" t="str">
+        <f>links!B13</f>
+        <v>/categories/ecosystem-programs</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" t="str">
+        <f>links!B14</f>
+        <v>/goals/launch-startup</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" t="str">
+        <f>links!B15</f>
+        <v>/goals/grow-existing-business</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" t="str">
+        <f>links!B16</f>
+        <v>/goals/support-entrepreneurship</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" t="str">
+        <f>links!B17</f>
+        <v>/goals/launch-startup</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" t="str">
+        <f>links!B18</f>
+        <v>/goals/mentoring-business</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/a/links_ cfe.xlsx
+++ b/a/links_ cfe.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="32">
   <si>
     <t>insert_url</t>
   </si>
@@ -106,6 +106,12 @@
   </si>
   <si>
     <t>Participants</t>
+  </si>
+  <si>
+    <t>testlink</t>
+  </si>
+  <si>
+    <t>https://cfeglobal.org/blog/winner-announced-in-the-2004-entrepreneur-of-the-year-contest-2004-11-26</t>
   </si>
 </sst>
 </file>
@@ -607,7 +613,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="3" width="17.54296875" customWidth="1"/>
@@ -615,7 +621,7 @@
     <col min="8" max="8" width="11.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>22</v>
       </c>
@@ -640,26 +646,32 @@
       <c r="H1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="str">
         <f>links!B2</f>
         <v>/programs/startup-huddle</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="str">
         <f>links!B3</f>
         <v>/programs/global-entrepreneurship-week</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="str">
         <f>links!B4</f>
         <v>/programs/young-entrepreneurs-alliance</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="str">
         <f>links!B5</f>
         <v>/programs/dynamic-entrepreneurship-classroom</v>
@@ -677,67 +689,67 @@
         <v>460</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="str">
         <f>links!B6</f>
         <v>/programs/scaleup-acceleration-program</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="str">
         <f>links!B7</f>
         <v>/programs/scaleup-club</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="str">
         <f>links!B8</f>
         <v>/programs/startup-club</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="str">
         <f>links!B9</f>
         <v>/programs/fasttrac</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="str">
         <f>links!B10</f>
         <v>/categories/acceleration-programs</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="str">
         <f>links!B11</f>
         <v>/categories/startup-programs</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="str">
         <f>links!B12</f>
         <v>/categories/educational-programs</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="str">
         <f>links!B13</f>
         <v>/categories/ecosystem-programs</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="str">
         <f>links!B14</f>
         <v>/goals/launch-startup</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="str">
         <f>links!B15</f>
         <v>/goals/grow-existing-business</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="str">
         <f>links!B16</f>
         <v>/goals/support-entrepreneurship</v>

--- a/a/links_ cfe.xlsx
+++ b/a/links_ cfe.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="120" windowWidth="19140" windowHeight="6840" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="120" windowWidth="19140" windowHeight="6840"/>
   </bookViews>
   <sheets>
     <sheet name="links" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="31">
   <si>
     <t>insert_url</t>
   </si>
@@ -39,9 +39,6 @@
     <t>/programs/scaleup-club</t>
   </si>
   <si>
-    <t>program_category</t>
-  </si>
-  <si>
     <t>/programs/startup-club</t>
   </si>
   <si>
@@ -54,18 +51,6 @@
     <t>/programs/fasttrac</t>
   </si>
   <si>
-    <t>/categories/acceleration-programs</t>
-  </si>
-  <si>
-    <t>/categories/startup-programs</t>
-  </si>
-  <si>
-    <t>/categories/educational-programs</t>
-  </si>
-  <si>
-    <t>/categories/ecosystem-programs</t>
-  </si>
-  <si>
     <t>/goals/grow-existing-business</t>
   </si>
   <si>
@@ -112,6 +97,18 @@
   </si>
   <si>
     <t>https://cfeglobal.org/blog/winner-announced-in-the-2004-entrepreneur-of-the-year-contest-2004-11-26</t>
+  </si>
+  <si>
+    <t>/programs/acceleration-programs</t>
+  </si>
+  <si>
+    <t>/programs/startup-programs</t>
+  </si>
+  <si>
+    <t>/programs/educational-programs</t>
+  </si>
+  <si>
+    <t>/programs/ecosystem-programs</t>
   </si>
 </sst>
 </file>
@@ -459,7 +456,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -467,7 +464,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
@@ -475,7 +472,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
@@ -483,7 +480,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
@@ -491,7 +488,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>4</v>
@@ -499,7 +496,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>5</v>
@@ -507,7 +504,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>6</v>
@@ -515,95 +512,95 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -623,31 +620,31 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" t="s">
-        <v>27</v>
-      </c>
       <c r="C1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" t="s">
         <v>24</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>25</v>
-      </c>
-      <c r="G1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
@@ -656,7 +653,7 @@
         <v>/programs/startup-huddle</v>
       </c>
       <c r="I2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
@@ -716,25 +713,25 @@
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="str">
         <f>links!B10</f>
-        <v>/categories/acceleration-programs</v>
+        <v>/programs/acceleration-programs</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="str">
         <f>links!B11</f>
-        <v>/categories/startup-programs</v>
+        <v>/programs/startup-programs</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="str">
         <f>links!B12</f>
-        <v>/categories/educational-programs</v>
+        <v>/programs/educational-programs</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="str">
         <f>links!B13</f>
-        <v>/categories/ecosystem-programs</v>
+        <v>/programs/ecosystem-programs</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">

--- a/a/links_ cfe.xlsx
+++ b/a/links_ cfe.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="32">
   <si>
     <t>insert_url</t>
   </si>
@@ -66,9 +66,6 @@
     <t>topic</t>
   </si>
   <si>
-    <t>partner</t>
-  </si>
-  <si>
     <t>Url</t>
   </si>
   <si>
@@ -109,6 +106,12 @@
   </si>
   <si>
     <t>/programs/ecosystem-programs</t>
+  </si>
+  <si>
+    <t>/programs/mentoring-programs</t>
+  </si>
+  <si>
+    <t>/programs/scale-up-programs</t>
   </si>
 </sst>
 </file>
@@ -447,7 +450,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.453125" customWidth="1"/>
@@ -531,7 +534,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -539,7 +542,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -547,7 +550,7 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
@@ -555,7 +558,7 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
@@ -600,11 +603,23 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>8</v>
+      </c>
+      <c r="B19" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -620,31 +635,31 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" t="s">
         <v>23</v>
       </c>
-      <c r="D1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>24</v>
-      </c>
-      <c r="I1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
@@ -653,7 +668,7 @@
         <v>/programs/startup-huddle</v>
       </c>
       <c r="I2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">

--- a/a/links_ cfe.xlsx
+++ b/a/links_ cfe.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="32">
   <si>
     <t>insert_url</t>
   </si>
@@ -45,24 +45,9 @@
     <t>program</t>
   </si>
   <si>
-    <t>goals</t>
-  </si>
-  <si>
     <t>/programs/fasttrac</t>
   </si>
   <si>
-    <t>/goals/grow-existing-business</t>
-  </si>
-  <si>
-    <t>/goals/launch-startup</t>
-  </si>
-  <si>
-    <t>/goals/support-entrepreneurship</t>
-  </si>
-  <si>
-    <t>/goals/mentoring-business</t>
-  </si>
-  <si>
     <t>topic</t>
   </si>
   <si>
@@ -112,6 +97,21 @@
   </si>
   <si>
     <t>/programs/scale-up-programs</t>
+  </si>
+  <si>
+    <t>/programs/launch-startup</t>
+  </si>
+  <si>
+    <t>/programs/grow-existing-business</t>
+  </si>
+  <si>
+    <t>/programs/support-entrepreneurship</t>
+  </si>
+  <si>
+    <t>/programs/mentoring-business</t>
+  </si>
+  <si>
+    <t>/programs/best-practices</t>
   </si>
 </sst>
 </file>
@@ -450,7 +450,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.453125" customWidth="1"/>
@@ -459,7 +459,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -526,7 +526,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
@@ -534,7 +534,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -542,7 +542,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -550,7 +550,7 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
@@ -558,47 +558,47 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
@@ -606,7 +606,7 @@
         <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
@@ -614,6 +614,14 @@
         <v>8</v>
       </c>
       <c r="B20" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" t="s">
         <v>31</v>
       </c>
     </row>
@@ -635,31 +643,31 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" t="s">
-        <v>21</v>
-      </c>
       <c r="C1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" t="s">
         <v>18</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>19</v>
-      </c>
-      <c r="G1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
@@ -668,7 +676,7 @@
         <v>/programs/startup-huddle</v>
       </c>
       <c r="I2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
@@ -752,31 +760,31 @@
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="str">
         <f>links!B14</f>
-        <v>/goals/launch-startup</v>
+        <v>/programs/launch-startup</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="str">
         <f>links!B15</f>
-        <v>/goals/grow-existing-business</v>
+        <v>/programs/grow-existing-business</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="str">
         <f>links!B16</f>
-        <v>/goals/support-entrepreneurship</v>
+        <v>/programs/support-entrepreneurship</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" t="str">
         <f>links!B17</f>
-        <v>/goals/launch-startup</v>
+        <v>/programs/launch-startup</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" t="str">
         <f>links!B18</f>
-        <v>/goals/mentoring-business</v>
+        <v>/programs/mentoring-business</v>
       </c>
     </row>
   </sheetData>

--- a/a/links_ cfe.xlsx
+++ b/a/links_ cfe.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="33">
   <si>
     <t>insert_url</t>
   </si>
@@ -112,6 +112,9 @@
   </si>
   <si>
     <t>/programs/best-practices</t>
+  </si>
+  <si>
+    <t>/programs/learn-entrepreneurship</t>
   </si>
 </sst>
 </file>
@@ -450,7 +453,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.453125" customWidth="1"/>
@@ -623,6 +626,14 @@
       </c>
       <c r="B21" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/a/links_ cfe.xlsx
+++ b/a/links_ cfe.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="37">
   <si>
     <t>insert_url</t>
   </si>
@@ -115,6 +115,18 @@
   </si>
   <si>
     <t>/programs/learn-entrepreneurship</t>
+  </si>
+  <si>
+    <t>/partners/ewing-marion-kauffman-foundation</t>
+  </si>
+  <si>
+    <t>/partners/global-entrepreneurship-network</t>
+  </si>
+  <si>
+    <t>/partners/us-department-of-state</t>
+  </si>
+  <si>
+    <t>partners</t>
   </si>
 </sst>
 </file>
@@ -453,7 +465,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.453125" customWidth="1"/>
@@ -634,6 +646,30 @@
       </c>
       <c r="B22" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/a/links_ cfe.xlsx
+++ b/a/links_ cfe.xlsx
@@ -27,9 +27,6 @@
     <t>/programs/global-entrepreneurship-week</t>
   </si>
   <si>
-    <t>/programs/young-entrepreneurs-alliance</t>
-  </si>
-  <si>
     <t>/programs/dynamic-entrepreneurship-classroom</t>
   </si>
   <si>
@@ -127,6 +124,9 @@
   </si>
   <si>
     <t>partners</t>
+  </si>
+  <si>
+    <t>/programs/g20-young-entrepreneurs-alliance</t>
   </si>
 </sst>
 </file>
@@ -474,7 +474,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
@@ -498,178 +498,178 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
         <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -690,31 +690,31 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
         <v>11</v>
       </c>
-      <c r="B1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" t="s">
         <v>17</v>
       </c>
-      <c r="D1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>18</v>
-      </c>
-      <c r="I1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
@@ -723,7 +723,7 @@
         <v>/programs/startup-huddle</v>
       </c>
       <c r="I2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
@@ -735,7 +735,7 @@
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="str">
         <f>links!B4</f>
-        <v>/programs/young-entrepreneurs-alliance</v>
+        <v>/programs/g20-young-entrepreneurs-alliance</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">

--- a/a/links_ cfe.xlsx
+++ b/a/links_ cfe.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="38">
   <si>
     <t>insert_url</t>
   </si>
@@ -127,6 +127,9 @@
   </si>
   <si>
     <t>/programs/g20-young-entrepreneurs-alliance</t>
+  </si>
+  <si>
+    <t>needs_update</t>
   </si>
 </sst>
 </file>
@@ -465,22 +468,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.453125" customWidth="1"/>
-    <col min="2" max="2" width="37.453125" customWidth="1"/>
+    <col min="2" max="2" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>9</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -488,7 +494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -496,7 +502,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -504,7 +510,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -512,7 +518,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -520,7 +526,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -528,7 +534,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -536,7 +542,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -544,7 +550,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -552,7 +558,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -560,7 +566,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -568,7 +574,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -576,7 +582,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -584,7 +590,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -592,7 +598,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>7</v>
       </c>
